--- a/evals/unit_tests_comparative/test01_moe_fused_vs_unfused/analysis_output_ref/perf_report_trace1.xlsx
+++ b/evals/unit_tests_comparative/test01_moe_fused_vs_unfused/analysis_output_ref/perf_report_trace1.xlsx
@@ -11,8 +11,9 @@
     <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="diff_stats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="unified_perf_callstacks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unified_perf_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="diff_stats" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1377,677 +1378,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>process_name</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>process_label</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>thread_name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Input Dims</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Input type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Input Strides</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ex_UID</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>operation_count</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>total_duration_us</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>mean_duration_us</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>std_duration_us</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_mean</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_std</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>speedup (trace2/trace1)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>delta_us (trace2 - trace1)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>lca_kernel_count_trace2</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>lca_id</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>lca_name</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>lca_total_kernel_time_trace1_us</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>lca_total_kernel_time_trace2_us</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_median</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_min</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>duration_us_max</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_median</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_min</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_max</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>kernel_details_summary</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>trunc_kernel_details</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>perf_params</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>has_perf_model</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Percentage (%)</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Cumulative Percentage (%)</t>
+          <t>call_stack</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>aiter::ck_moe_stage1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>MoE_unfused</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>((4096, 8192), (8, 8192, 22016))</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>('c10::bfloat16', 'c10::bfloat16')</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K2" t="n">
+          <t>aiter::ck_moe_stage1 =&gt; aiter::ck_moe_stage1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>20</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>480</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>480</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.6896551724137931</v>
-      </c>
-      <c r="S2" t="n">
-        <v>320</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>moe_layer</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>1160</v>
-      </c>
-      <c r="X2" t="n">
-        <v>800</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>480</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>480</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>480</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[{'name': 'ck_moe_stage1_kernel&lt;BF16, 128, 128&gt;', 'stream': 0, 'gpu_op_uid': 11, 'count': 1, 'total_duration_us': np.float64(480.0), 'gpu_op_uids': [11], 'mean_duration_us': np.float64(480.0), 'median_duration_us': np.float64(480.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(480.0), 'max_duration_us': np.float64(480.0)}]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[{'name': 'ck_moe_stage1_kernel&lt;BF16, 128, 128&gt;', 'stream': 0, 'mean_duration_us': np.float64(480.0)}]</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>41.37931034482759</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>41.37931034482759</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>aiter::ck_moe_stage2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>MoE_unfused</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>((4096, 8192), (8, 8192, 22016))</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>('c10::bfloat16', 'c10::bfloat16')</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>20</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>480</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
-        <v>480</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.6896551724137931</v>
-      </c>
-      <c r="S3" t="n">
-        <v>320</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>moe_layer</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>1160</v>
-      </c>
-      <c r="X3" t="n">
-        <v>800</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>480</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>480</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>480</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[{'name': 'ck_moe_stage2_kernel&lt;BF16, 128, 128&gt;', 'stream': 0, 'gpu_op_uid': 16, 'count': 1, 'total_duration_us': np.float64(480.0), 'gpu_op_uids': [16], 'mean_duration_us': np.float64(480.0), 'median_duration_us': np.float64(480.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(480.0), 'max_duration_us': np.float64(480.0)}]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[{'name': 'ck_moe_stage2_kernel&lt;BF16, 128, 128&gt;', 'stream': 0, 'mean_duration_us': np.float64(480.0)}]</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>41.37931034482759</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>82.75862068965517</v>
+          <t>aiter::ck_moe_stage2 =&gt; aiter::ck_moe_stage2</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>aiter::moe_sorting_fwd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>MoE_aux</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>((4096, 8192), (8, 8192, 22016))</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>('c10::bfloat16', 'c10::bfloat16')</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>20</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>120</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>120</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.6896551724137931</v>
-      </c>
-      <c r="S4" t="n">
-        <v>680</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>moe_layer</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>1160</v>
-      </c>
-      <c r="X4" t="n">
-        <v>800</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[{'name': 'moe_sorting_kernel&lt;BF16&gt;', 'stream': 0, 'gpu_op_uid': 6, 'count': 1, 'total_duration_us': np.float64(120.0), 'gpu_op_uids': [6], 'mean_duration_us': np.float64(120.0), 'median_duration_us': np.float64(120.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(120.0), 'max_duration_us': np.float64(120.0)}]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[{'name': 'moe_sorting_kernel&lt;BF16&gt;', 'stream': 0, 'mean_duration_us': np.float64(120.0)}]</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>10.3448275862069</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>93.10344827586206</v>
+          <t>aiter::moe_sorting_fwd =&gt; aiter::moe_sorting_fwd</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>aiter::moe_sum</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>MoE_aux</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>((4096, 8192), (8, 8192, 22016))</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>('c10::bfloat16', 'c10::bfloat16')</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>20</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>80</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>80</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.6896551724137931</v>
-      </c>
-      <c r="S5" t="n">
-        <v>720</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>moe_layer</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>1160</v>
-      </c>
-      <c r="X5" t="n">
-        <v>800</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[{'name': 'moe_sum_kernel&lt;BF16&gt;', 'stream': 0, 'gpu_op_uid': 21, 'count': 1, 'total_duration_us': np.float64(80.0), 'gpu_op_uids': [21], 'mean_duration_us': np.float64(80.0), 'median_duration_us': np.float64(80.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(80.0), 'max_duration_us': np.float64(80.0)}]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[{'name': 'moe_sum_kernel&lt;BF16&gt;', 'stream': 0, 'mean_duration_us': np.float64(80.0)}]</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.896551724137931</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>100</v>
+          <t>aiter::moe_sum =&gt; aiter::moe_sum</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2061,6 +1494,715 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AK5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>op category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>process_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>process_label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Input type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ex_UID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>operation_count</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>total_duration_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mean_duration_us</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>std_duration_us</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>speedup (trace2/trace1)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>delta_us (trace2 - trace1)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>lca_count_trace2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>lca_id</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>lca_name</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>lca_total_kernel_time_trace1_us</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>lca_total_kernel_time_trace2_us</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_median</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_min</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>duration_us_max</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details_summary</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>perf_params</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>has_perf_model</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_call_stack</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Percentage (%)</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative Percentage (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aiter::ck_moe_stage1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MoE_unfused</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>((4096, 8192), (8, 8192, 22016))</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>('c10::bfloat16', 'c10::bfloat16')</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>480</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>480</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="S2" t="n">
+        <v>320</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>moe_layer</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1160</v>
+      </c>
+      <c r="X2" t="n">
+        <v>800</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>480</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>480</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[{'name': 'ck_moe_stage1_kernel&lt;BF16, 128, 128&gt;', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(480.0), 'gpu_op_uids': [11], 'mean_duration_us': np.float64(480.0), 'median_duration_us': np.float64(480.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(480.0), 'max_duration_us': np.float64(480.0)}]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[{'name': 'ck_moe_stage1_kernel&lt;BF16, 128, 128&gt;', 'stream': 0, 'mean_duration_us': np.float64(480.0)}]</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>aiter::ck_moe_stage1 =&gt; aiter::ck_moe_stage1</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>41.37931034482759</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>41.37931034482759</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aiter::ck_moe_stage2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MoE_unfused</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>((4096, 8192), (8, 8192, 22016))</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>('c10::bfloat16', 'c10::bfloat16')</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>480</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>480</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="S3" t="n">
+        <v>320</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>moe_layer</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1160</v>
+      </c>
+      <c r="X3" t="n">
+        <v>800</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>480</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>480</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>480</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[{'name': 'ck_moe_stage2_kernel&lt;BF16, 128, 128&gt;', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(480.0), 'gpu_op_uids': [16], 'mean_duration_us': np.float64(480.0), 'median_duration_us': np.float64(480.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(480.0), 'max_duration_us': np.float64(480.0)}]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[{'name': 'ck_moe_stage2_kernel&lt;BF16, 128, 128&gt;', 'stream': 0, 'mean_duration_us': np.float64(480.0)}]</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>aiter::ck_moe_stage2 =&gt; aiter::ck_moe_stage2</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>41.37931034482759</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>82.75862068965517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aiter::moe_sorting_fwd</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MoE_aux</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>((4096, 8192), (8, 8192, 22016))</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>('c10::bfloat16', 'c10::bfloat16')</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>20</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>120</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>120</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="S4" t="n">
+        <v>680</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>moe_layer</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="X4" t="n">
+        <v>800</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[{'name': 'moe_sorting_kernel&lt;BF16&gt;', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(120.0), 'gpu_op_uids': [6], 'mean_duration_us': np.float64(120.0), 'median_duration_us': np.float64(120.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(120.0), 'max_duration_us': np.float64(120.0)}]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[{'name': 'moe_sorting_kernel&lt;BF16&gt;', 'stream': 0, 'mean_duration_us': np.float64(120.0)}]</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>aiter::moe_sorting_fwd =&gt; aiter::moe_sorting_fwd</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>10.3448275862069</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>93.10344827586206</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aiter::moe_sum</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MoE_aux</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>((4096, 8192), (8, 8192, 22016))</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>('c10::bfloat16', 'c10::bfloat16')</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>80</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>80</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="S5" t="n">
+        <v>720</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>moe_layer</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1160</v>
+      </c>
+      <c r="X5" t="n">
+        <v>800</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[{'name': 'moe_sum_kernel&lt;BF16&gt;', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(80.0), 'gpu_op_uids': [21], 'mean_duration_us': np.float64(80.0), 'median_duration_us': np.float64(80.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(80.0), 'max_duration_us': np.float64(80.0)}]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[{'name': 'moe_sum_kernel&lt;BF16&gt;', 'stream': 0, 'mean_duration_us': np.float64(80.0)}]</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>aiter::moe_sum =&gt; aiter::moe_sum</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>6.896551724137931</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
